--- a/backend/data/financials_by_company/1107.HK.xlsx
+++ b/backend/data/financials_by_company/1107.HK.xlsx
@@ -662,55 +662,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-343614250</v>
+        <v>-96172000</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>-3510405000</v>
+        <v>-749788000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1374457000</v>
+        <v>-384688000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1374457000</v>
+        <v>-384688000</v>
       </c>
       <c r="G2" t="n">
-        <v>-7458758000</v>
+        <v>-2054632000</v>
       </c>
       <c r="H2" t="n">
-        <v>43067000</v>
+        <v>23989000</v>
       </c>
       <c r="I2" t="n">
-        <v>3588883000</v>
+        <v>10795503000</v>
       </c>
       <c r="J2" t="n">
-        <v>-4884862000</v>
+        <v>-1134476000</v>
       </c>
       <c r="K2" t="n">
-        <v>-4927929000</v>
+        <v>-1158465000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2216458000</v>
+        <v>-336032000</v>
       </c>
       <c r="M2" t="n">
-        <v>2234475000</v>
+        <v>403997000</v>
       </c>
       <c r="N2" t="n">
-        <v>18017000</v>
+        <v>67965000</v>
       </c>
       <c r="O2" t="n">
-        <v>-6427915250</v>
+        <v>-1766116000</v>
       </c>
       <c r="P2" t="n">
-        <v>-7458758000</v>
+        <v>-2054632000</v>
       </c>
       <c r="Q2" t="n">
-        <v>6117402000</v>
+        <v>12432507000</v>
       </c>
       <c r="R2" t="n">
         <v>2794994000</v>
@@ -719,144 +719,142 @@
         <v>2794994000</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.669</v>
+        <v>-0.735</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.669</v>
+        <v>-0.735</v>
       </c>
       <c r="V2" t="n">
-        <v>-7458758000</v>
+        <v>-2054632000</v>
       </c>
       <c r="W2" t="n">
-        <v>-7458758000</v>
+        <v>-2054632000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-7458758000</v>
+        <v>-2054632000</v>
       </c>
       <c r="Z2" t="n">
-        <v>101058000</v>
+        <v>275124000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-7559816000</v>
+        <v>-2329756000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-7559816000</v>
+        <v>-2329756000</v>
       </c>
       <c r="AC2" t="n">
-        <v>397412000</v>
+        <v>767294000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-7162404000</v>
+        <v>-1562462000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-18072000</v>
+        <v>-40141000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1374457000</v>
+        <v>-384688000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1374457000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
+        <v>384688000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2216458000</v>
+        <v>-336032000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2234475000</v>
+        <v>403997000</v>
       </c>
       <c r="AL2" t="n">
-        <v>18017000</v>
+        <v>67965000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2984090000</v>
+        <v>-982886000</v>
       </c>
       <c r="AN2" t="n">
-        <v>2528519000</v>
+        <v>1637004000</v>
       </c>
       <c r="AO2" t="n">
-        <v>2225755000</v>
+        <v>317658000</v>
       </c>
       <c r="AP2" t="n">
-        <v>302813000</v>
+        <v>1336230000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>118730000</v>
+        <v>665434000</v>
       </c>
       <c r="AR2" t="n">
-        <v>184083000</v>
+        <v>670796000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-455571000</v>
+        <v>654118000</v>
       </c>
       <c r="AT2" t="n">
-        <v>3588883000</v>
+        <v>10795503000</v>
       </c>
       <c r="AU2" t="n">
-        <v>3133312000</v>
+        <v>11449621000</v>
       </c>
       <c r="AV2" t="n">
-        <v>3133312000</v>
+        <v>11449621000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-457106750</v>
+        <v>-223240750</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-10820829000</v>
+        <v>-3375555000</v>
       </c>
       <c r="E3" t="n">
-        <v>-1828427000</v>
+        <v>-892963000</v>
       </c>
       <c r="F3" t="n">
-        <v>-1828427000</v>
+        <v>-892963000</v>
       </c>
       <c r="G3" t="n">
-        <v>-14312777000</v>
+        <v>-4453718000</v>
       </c>
       <c r="H3" t="n">
-        <v>27169000</v>
+        <v>22592000</v>
       </c>
       <c r="I3" t="n">
-        <v>10147850000</v>
+        <v>6718744000</v>
       </c>
       <c r="J3" t="n">
-        <v>-12649256000</v>
+        <v>-4268518000</v>
       </c>
       <c r="K3" t="n">
-        <v>-12676425000</v>
+        <v>-4291110000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2833871000</v>
+        <v>-365373000</v>
       </c>
       <c r="M3" t="n">
-        <v>2852953000</v>
+        <v>375693000</v>
       </c>
       <c r="N3" t="n">
-        <v>19082000</v>
+        <v>10320000</v>
       </c>
       <c r="O3" t="n">
-        <v>-12941456750</v>
+        <v>-3783995750</v>
       </c>
       <c r="P3" t="n">
-        <v>-14312777000</v>
+        <v>-4453718000</v>
       </c>
       <c r="Q3" t="n">
-        <v>16283326000</v>
+        <v>7916687000</v>
       </c>
       <c r="R3" t="n">
         <v>2794994000</v>
@@ -865,144 +863,142 @@
         <v>2794994000</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.121</v>
+        <v>-1.594</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.121</v>
+        <v>-1.594</v>
       </c>
       <c r="V3" t="n">
-        <v>-14312777000</v>
+        <v>-4453718000</v>
       </c>
       <c r="W3" t="n">
-        <v>-14312777000</v>
+        <v>-4453718000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-14312777000</v>
+        <v>-4453718000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1575110000</v>
+        <v>451251000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-15887887000</v>
+        <v>-4904969000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-15887887000</v>
+        <v>-4904969000</v>
       </c>
       <c r="AC3" t="n">
-        <v>358509000</v>
+        <v>238166000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-15529378000</v>
+        <v>-4666803000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-48176000</v>
+        <v>-23750000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1828427000</v>
+        <v>-892963000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1605272000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>367221000</v>
-      </c>
+        <v>1390018000</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>-144066000</v>
+        <v>-497055000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-2833871000</v>
+        <v>-365373000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2852953000</v>
+        <v>375693000</v>
       </c>
       <c r="AL3" t="n">
-        <v>19082000</v>
+        <v>10320000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-10579580000</v>
+        <v>-2312822000</v>
       </c>
       <c r="AN3" t="n">
-        <v>6135476000</v>
+        <v>1197943000</v>
       </c>
       <c r="AO3" t="n">
-        <v>5567791000</v>
+        <v>401437000</v>
       </c>
       <c r="AP3" t="n">
-        <v>567937000</v>
+        <v>797637000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>311585000</v>
+        <v>373115000</v>
       </c>
       <c r="AR3" t="n">
-        <v>256352000</v>
+        <v>424522000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-4444104000</v>
+        <v>-1114879000</v>
       </c>
       <c r="AT3" t="n">
-        <v>10147850000</v>
+        <v>6718744000</v>
       </c>
       <c r="AU3" t="n">
-        <v>5703746000</v>
+        <v>5603865000</v>
       </c>
       <c r="AV3" t="n">
-        <v>5703746000</v>
+        <v>5603865000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-223240750</v>
+        <v>-457106750</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-3375555000</v>
+        <v>-10820829000</v>
       </c>
       <c r="E4" t="n">
-        <v>-892963000</v>
+        <v>-1828427000</v>
       </c>
       <c r="F4" t="n">
-        <v>-892963000</v>
+        <v>-1828427000</v>
       </c>
       <c r="G4" t="n">
-        <v>-4453718000</v>
+        <v>-14312777000</v>
       </c>
       <c r="H4" t="n">
-        <v>22592000</v>
+        <v>27169000</v>
       </c>
       <c r="I4" t="n">
-        <v>6718744000</v>
+        <v>10147850000</v>
       </c>
       <c r="J4" t="n">
-        <v>-4268518000</v>
+        <v>-12649256000</v>
       </c>
       <c r="K4" t="n">
-        <v>-4291110000</v>
+        <v>-12676425000</v>
       </c>
       <c r="L4" t="n">
-        <v>-365373000</v>
+        <v>-2833871000</v>
       </c>
       <c r="M4" t="n">
-        <v>375693000</v>
+        <v>2852953000</v>
       </c>
       <c r="N4" t="n">
-        <v>10320000</v>
+        <v>19082000</v>
       </c>
       <c r="O4" t="n">
-        <v>-3783995750</v>
+        <v>-12941456750</v>
       </c>
       <c r="P4" t="n">
-        <v>-4453718000</v>
+        <v>-14312777000</v>
       </c>
       <c r="Q4" t="n">
-        <v>7916687000</v>
+        <v>16283326000</v>
       </c>
       <c r="R4" t="n">
         <v>2794994000</v>
@@ -1011,142 +1007,144 @@
         <v>2794994000</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.594</v>
+        <v>-5.121</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.594</v>
+        <v>-5.121</v>
       </c>
       <c r="V4" t="n">
-        <v>-4453718000</v>
+        <v>-14312777000</v>
       </c>
       <c r="W4" t="n">
-        <v>-4453718000</v>
+        <v>-14312777000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-4453718000</v>
+        <v>-14312777000</v>
       </c>
       <c r="Z4" t="n">
-        <v>451251000</v>
+        <v>1575110000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4904969000</v>
+        <v>-15887887000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-4904969000</v>
+        <v>-15887887000</v>
       </c>
       <c r="AC4" t="n">
-        <v>238166000</v>
+        <v>358509000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-4666803000</v>
+        <v>-15529378000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-23750000</v>
+        <v>-48176000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-892963000</v>
+        <v>-1828427000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1390018000</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>1605272000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>367221000</v>
+      </c>
       <c r="AI4" t="n">
-        <v>-497055000</v>
+        <v>-144066000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-365373000</v>
+        <v>-2833871000</v>
       </c>
       <c r="AK4" t="n">
-        <v>375693000</v>
+        <v>2852953000</v>
       </c>
       <c r="AL4" t="n">
-        <v>10320000</v>
+        <v>19082000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-2312822000</v>
+        <v>-10579580000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1197943000</v>
+        <v>6135476000</v>
       </c>
       <c r="AO4" t="n">
-        <v>401437000</v>
+        <v>5567791000</v>
       </c>
       <c r="AP4" t="n">
-        <v>797637000</v>
+        <v>567937000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>373115000</v>
+        <v>311585000</v>
       </c>
       <c r="AR4" t="n">
-        <v>424522000</v>
+        <v>256352000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1114879000</v>
+        <v>-4444104000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6718744000</v>
+        <v>10147850000</v>
       </c>
       <c r="AU4" t="n">
-        <v>5603865000</v>
+        <v>5703746000</v>
       </c>
       <c r="AV4" t="n">
-        <v>5603865000</v>
+        <v>5703746000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-96172000</v>
+        <v>-343614250</v>
       </c>
       <c r="C5" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>-749788000</v>
+        <v>-3510405000</v>
       </c>
       <c r="E5" t="n">
-        <v>-384688000</v>
+        <v>-1374457000</v>
       </c>
       <c r="F5" t="n">
-        <v>-384688000</v>
+        <v>-1374457000</v>
       </c>
       <c r="G5" t="n">
-        <v>-2054632000</v>
+        <v>-7458758000</v>
       </c>
       <c r="H5" t="n">
-        <v>23989000</v>
+        <v>43067000</v>
       </c>
       <c r="I5" t="n">
-        <v>10795503000</v>
+        <v>3588883000</v>
       </c>
       <c r="J5" t="n">
-        <v>-1134476000</v>
+        <v>-4884862000</v>
       </c>
       <c r="K5" t="n">
-        <v>-1158465000</v>
+        <v>-4927929000</v>
       </c>
       <c r="L5" t="n">
-        <v>-336032000</v>
+        <v>-2216458000</v>
       </c>
       <c r="M5" t="n">
-        <v>403997000</v>
+        <v>2234475000</v>
       </c>
       <c r="N5" t="n">
-        <v>67965000</v>
+        <v>18017000</v>
       </c>
       <c r="O5" t="n">
-        <v>-1766116000</v>
+        <v>-6427915250</v>
       </c>
       <c r="P5" t="n">
-        <v>-2054632000</v>
+        <v>-7458758000</v>
       </c>
       <c r="Q5" t="n">
-        <v>12432507000</v>
+        <v>6117402000</v>
       </c>
       <c r="R5" t="n">
         <v>2794994000</v>
@@ -1155,89 +1153,91 @@
         <v>2794994000</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.735</v>
+        <v>-2.669</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.735</v>
+        <v>-2.669</v>
       </c>
       <c r="V5" t="n">
-        <v>-2054632000</v>
+        <v>-7458758000</v>
       </c>
       <c r="W5" t="n">
-        <v>-2054632000</v>
+        <v>-7458758000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-2054632000</v>
+        <v>-7458758000</v>
       </c>
       <c r="Z5" t="n">
-        <v>275124000</v>
+        <v>101058000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-2329756000</v>
+        <v>-7559816000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2329756000</v>
+        <v>-7559816000</v>
       </c>
       <c r="AC5" t="n">
-        <v>767294000</v>
+        <v>397412000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1562462000</v>
+        <v>-7162404000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-40141000</v>
+        <v>-18072000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-384688000</v>
+        <v>-1374457000</v>
       </c>
       <c r="AG5" t="n">
-        <v>384688000</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>1374457000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-336032000</v>
+        <v>-2216458000</v>
       </c>
       <c r="AK5" t="n">
-        <v>403997000</v>
+        <v>2234475000</v>
       </c>
       <c r="AL5" t="n">
-        <v>67965000</v>
+        <v>18017000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-982886000</v>
+        <v>-2984090000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1637004000</v>
+        <v>2528519000</v>
       </c>
       <c r="AO5" t="n">
-        <v>317658000</v>
+        <v>2225755000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1336230000</v>
+        <v>302813000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>665434000</v>
+        <v>118730000</v>
       </c>
       <c r="AR5" t="n">
-        <v>670796000</v>
+        <v>184083000</v>
       </c>
       <c r="AS5" t="n">
-        <v>654118000</v>
+        <v>-455571000</v>
       </c>
       <c r="AT5" t="n">
-        <v>10795503000</v>
+        <v>3588883000</v>
       </c>
       <c r="AU5" t="n">
-        <v>11449621000</v>
+        <v>3133312000</v>
       </c>
       <c r="AV5" t="n">
-        <v>11449621000</v>
+        <v>3133312000</v>
       </c>
     </row>
   </sheetData>
@@ -1568,55 +1568,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>2794994650</v>
+        <v>2794994000</v>
       </c>
       <c r="C2" t="n">
-        <v>2794994650</v>
+        <v>2794994000</v>
       </c>
       <c r="D2" t="n">
-        <v>23596991000</v>
+        <v>22961364000</v>
       </c>
       <c r="E2" t="n">
-        <v>23684157000</v>
+        <v>24546407000</v>
       </c>
       <c r="F2" t="n">
-        <v>-21999810000</v>
+        <v>4447107000</v>
       </c>
       <c r="G2" t="n">
-        <v>1704265000</v>
+        <v>29015288000</v>
       </c>
       <c r="H2" t="n">
-        <v>-26856906000</v>
+        <v>-4888821000</v>
       </c>
       <c r="I2" t="n">
-        <v>-21999810000</v>
+        <v>4447107000</v>
       </c>
       <c r="J2" t="n">
-        <v>-21979892000</v>
+        <v>4468881000</v>
       </c>
       <c r="K2" t="n">
-        <v>-20098575000</v>
+        <v>6376208000</v>
       </c>
       <c r="L2" t="n">
-        <v>-22649773000</v>
+        <v>6813355000</v>
       </c>
       <c r="M2" t="n">
-        <v>-669881000</v>
+        <v>2344474000</v>
       </c>
       <c r="N2" t="n">
-        <v>-21979892000</v>
+        <v>4468881000</v>
       </c>
       <c r="O2" t="n">
-        <v>5640000</v>
+        <v>8612000</v>
       </c>
       <c r="P2" t="n">
         <v>40060000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-23674252000</v>
+        <v>2599001000</v>
       </c>
       <c r="R2" t="n">
         <v>825711000</v>
@@ -1628,182 +1628,184 @@
         <v>175693000</v>
       </c>
       <c r="U2" t="n">
-        <v>58282481000</v>
+        <v>70805210000</v>
       </c>
       <c r="V2" t="n">
-        <v>2191988000</v>
+        <v>2560861000</v>
       </c>
       <c r="W2" t="n">
-        <v>310671000</v>
+        <v>653534000</v>
       </c>
       <c r="X2" t="n">
-        <v>1881317000</v>
+        <v>1907327000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1881317000</v>
+        <v>1907327000</v>
       </c>
       <c r="Z2" t="n">
-        <v>56090493000</v>
+        <v>68244349000</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>21802840000</v>
+        <v>22639080000</v>
       </c>
       <c r="AC2" t="n">
-        <v>21802840000</v>
+        <v>22639080000</v>
       </c>
       <c r="AD2" t="n">
-        <v>795384000</v>
+        <v>264315000</v>
       </c>
       <c r="AE2" t="n">
-        <v>22185256000</v>
+        <v>14561175000</v>
       </c>
       <c r="AF2" t="n">
-        <v>11638438000</v>
+        <v>7054457000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1458000</v>
+        <v>2898000</v>
       </c>
       <c r="AH2" t="n">
-        <v>5134435000</v>
+        <v>3940008000</v>
       </c>
       <c r="AI2" t="n">
-        <v>5410925000</v>
+        <v>3563812000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>35632708000</v>
+        <v>77618565000</v>
       </c>
       <c r="AK2" t="n">
-        <v>6399121000</v>
+        <v>14263037000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1022784000</v>
+        <v>1311796000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1883000</v>
+        <v>46083000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1883000</v>
+        <v>46083000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1778998000</v>
+        <v>2337834000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1751739000</v>
+        <v>2233385000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>27259000</v>
+        <v>104449000</v>
       </c>
       <c r="AR2" t="n">
-        <v>2010805000</v>
+        <v>3061710000</v>
       </c>
       <c r="AS2" t="n">
-        <v>19918000</v>
+        <v>21774000</v>
       </c>
       <c r="AT2" t="n">
-        <v>361409000</v>
+        <v>395700000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-248499000</v>
+        <v>-223764000</v>
       </c>
       <c r="AV2" t="n">
-        <v>609908000</v>
+        <v>619464000</v>
       </c>
       <c r="AW2" t="n">
-        <v>61590000</v>
+        <v>68348000</v>
       </c>
       <c r="AX2" t="n">
-        <v>548318000</v>
+        <v>551116000</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>29233587000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
+        <v>63355528000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>2947689000</v>
+      </c>
       <c r="BB2" t="n">
-        <v>250462000</v>
+        <v>2426926000</v>
       </c>
       <c r="BC2" t="n">
-        <v>2325834000</v>
+        <v>2975285000</v>
       </c>
       <c r="BD2" t="n">
-        <v>20295094000</v>
+        <v>45700454000</v>
       </c>
       <c r="BE2" t="n">
-        <v>610930000</v>
+        <v>1052545000</v>
       </c>
       <c r="BF2" t="n">
-        <v>19684164000</v>
+        <v>44647909000</v>
       </c>
       <c r="BG2" t="n">
-        <v>5875772000</v>
+        <v>7325917000</v>
       </c>
       <c r="BH2" t="n">
-        <v>399259000</v>
+        <v>394214000</v>
       </c>
       <c r="BI2" t="n">
-        <v>87166000</v>
+        <v>1585043000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>87166000</v>
+        <v>1585043000</v>
       </c>
       <c r="BK2" t="n">
-        <v>87166000</v>
+        <v>1585043000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2794994650</v>
+        <v>2794994000</v>
       </c>
       <c r="C3" t="n">
-        <v>2794994650</v>
+        <v>2794994000</v>
       </c>
       <c r="D3" t="n">
-        <v>22659692000</v>
+        <v>21620562000</v>
       </c>
       <c r="E3" t="n">
-        <v>22951604000</v>
+        <v>22162894000</v>
       </c>
       <c r="F3" t="n">
-        <v>-14536224000</v>
+        <v>-172527000</v>
       </c>
       <c r="G3" t="n">
-        <v>8436214000</v>
+        <v>22009980000</v>
       </c>
       <c r="H3" t="n">
-        <v>-9066516000</v>
+        <v>-1361796000</v>
       </c>
       <c r="I3" t="n">
-        <v>-14536224000</v>
+        <v>-172527000</v>
       </c>
       <c r="J3" t="n">
-        <v>-14515390000</v>
+        <v>-152914000</v>
       </c>
       <c r="K3" t="n">
-        <v>-2078045000</v>
+        <v>10564229000</v>
       </c>
       <c r="L3" t="n">
-        <v>-15158873000</v>
+        <v>871703000</v>
       </c>
       <c r="M3" t="n">
-        <v>-643483000</v>
+        <v>1024617000</v>
       </c>
       <c r="N3" t="n">
-        <v>-14515390000</v>
+        <v>-152914000</v>
       </c>
       <c r="O3" t="n">
-        <v>7573000</v>
+        <v>11163000</v>
       </c>
       <c r="P3" t="n">
         <v>40060000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-16215494000</v>
+        <v>-1902717000</v>
       </c>
       <c r="R3" t="n">
         <v>825711000</v>
@@ -1815,182 +1817,186 @@
         <v>175693000</v>
       </c>
       <c r="U3" t="n">
-        <v>57574195000</v>
+        <v>57628751000</v>
       </c>
       <c r="V3" t="n">
-        <v>12901231000</v>
+        <v>11196527000</v>
       </c>
       <c r="W3" t="n">
-        <v>463886000</v>
+        <v>479384000</v>
       </c>
       <c r="X3" t="n">
-        <v>12437345000</v>
+        <v>10717143000</v>
       </c>
       <c r="Y3" t="n">
-        <v>12437345000</v>
+        <v>10717143000</v>
       </c>
       <c r="Z3" t="n">
-        <v>44672964000</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+        <v>46432224000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
       <c r="AB3" t="n">
-        <v>10514259000</v>
+        <v>11445751000</v>
       </c>
       <c r="AC3" t="n">
-        <v>10514259000</v>
+        <v>11445751000</v>
       </c>
       <c r="AD3" t="n">
-        <v>765028000</v>
+        <v>497108000</v>
       </c>
       <c r="AE3" t="n">
-        <v>19266345000</v>
+        <v>12588023000</v>
       </c>
       <c r="AF3" t="n">
-        <v>10040268000</v>
+        <v>6902561000</v>
       </c>
       <c r="AG3" t="n">
-        <v>3212000</v>
+        <v>3166000</v>
       </c>
       <c r="AH3" t="n">
-        <v>4669717000</v>
+        <v>3826472000</v>
       </c>
       <c r="AI3" t="n">
-        <v>4553148000</v>
+        <v>1855824000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42415322000</v>
+        <v>58500454000</v>
       </c>
       <c r="AK3" t="n">
-        <v>6808874000</v>
+        <v>13430026000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1063212000</v>
+        <v>918404000</v>
       </c>
       <c r="AM3" t="n">
-        <v>580000</v>
+        <v>41360000</v>
       </c>
       <c r="AN3" t="n">
-        <v>580000</v>
+        <v>41360000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1701625000</v>
+        <v>2620851000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1673597000</v>
+        <v>2576293000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>28028000</v>
+        <v>44558000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2377500000</v>
+        <v>2794240000</v>
       </c>
       <c r="AS3" t="n">
-        <v>20834000</v>
+        <v>19613000</v>
       </c>
       <c r="AT3" t="n">
-        <v>383951000</v>
+        <v>362632000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-228563000</v>
+        <v>-212187000</v>
       </c>
       <c r="AV3" t="n">
-        <v>612514000</v>
+        <v>574819000</v>
       </c>
       <c r="AW3" t="n">
-        <v>62653000</v>
+        <v>63749000</v>
       </c>
       <c r="AX3" t="n">
-        <v>549861000</v>
+        <v>511070000</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>35606448000</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
+        <v>45070428000</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
       <c r="BB3" t="n">
-        <v>391073000</v>
+        <v>1027897000</v>
       </c>
       <c r="BC3" t="n">
-        <v>2379738000</v>
+        <v>2208568000</v>
       </c>
       <c r="BD3" t="n">
-        <v>24219391000</v>
+        <v>34599754000</v>
       </c>
       <c r="BE3" t="n">
-        <v>651151000</v>
+        <v>928644000</v>
       </c>
       <c r="BF3" t="n">
-        <v>23568240000</v>
+        <v>33671110000</v>
       </c>
       <c r="BG3" t="n">
-        <v>7934124000</v>
+        <v>6354946000</v>
       </c>
       <c r="BH3" t="n">
-        <v>390210000</v>
+        <v>336931000</v>
       </c>
       <c r="BI3" t="n">
-        <v>291912000</v>
+        <v>542332000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>291912000</v>
+        <v>542332000</v>
       </c>
       <c r="BK3" t="n">
-        <v>291912000</v>
+        <v>542332000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>2794994000</v>
+        <v>2794994650</v>
       </c>
       <c r="C4" t="n">
-        <v>2794994000</v>
+        <v>2794994650</v>
       </c>
       <c r="D4" t="n">
-        <v>21620562000</v>
+        <v>22659692000</v>
       </c>
       <c r="E4" t="n">
-        <v>22162894000</v>
+        <v>22951604000</v>
       </c>
       <c r="F4" t="n">
-        <v>-172527000</v>
+        <v>-14536224000</v>
       </c>
       <c r="G4" t="n">
-        <v>22009980000</v>
+        <v>8436214000</v>
       </c>
       <c r="H4" t="n">
-        <v>-1361796000</v>
+        <v>-9066516000</v>
       </c>
       <c r="I4" t="n">
-        <v>-172527000</v>
+        <v>-14536224000</v>
       </c>
       <c r="J4" t="n">
-        <v>-152914000</v>
+        <v>-14515390000</v>
       </c>
       <c r="K4" t="n">
-        <v>10564229000</v>
+        <v>-2078045000</v>
       </c>
       <c r="L4" t="n">
-        <v>871703000</v>
+        <v>-15158873000</v>
       </c>
       <c r="M4" t="n">
-        <v>1024617000</v>
+        <v>-643483000</v>
       </c>
       <c r="N4" t="n">
-        <v>-152914000</v>
+        <v>-14515390000</v>
       </c>
       <c r="O4" t="n">
-        <v>11163000</v>
+        <v>7573000</v>
       </c>
       <c r="P4" t="n">
         <v>40060000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1902717000</v>
+        <v>-16215494000</v>
       </c>
       <c r="R4" t="n">
         <v>825711000</v>
@@ -2002,186 +2008,182 @@
         <v>175693000</v>
       </c>
       <c r="U4" t="n">
-        <v>57628751000</v>
+        <v>57574195000</v>
       </c>
       <c r="V4" t="n">
-        <v>11196527000</v>
+        <v>12901231000</v>
       </c>
       <c r="W4" t="n">
-        <v>479384000</v>
+        <v>463886000</v>
       </c>
       <c r="X4" t="n">
-        <v>10717143000</v>
+        <v>12437345000</v>
       </c>
       <c r="Y4" t="n">
-        <v>10717143000</v>
+        <v>12437345000</v>
       </c>
       <c r="Z4" t="n">
-        <v>46432224000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
+        <v>44672964000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>11445751000</v>
+        <v>10514259000</v>
       </c>
       <c r="AC4" t="n">
-        <v>11445751000</v>
+        <v>10514259000</v>
       </c>
       <c r="AD4" t="n">
-        <v>497108000</v>
+        <v>765028000</v>
       </c>
       <c r="AE4" t="n">
-        <v>12588023000</v>
+        <v>19266345000</v>
       </c>
       <c r="AF4" t="n">
-        <v>6902561000</v>
+        <v>10040268000</v>
       </c>
       <c r="AG4" t="n">
-        <v>3166000</v>
+        <v>3212000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3826472000</v>
+        <v>4669717000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1855824000</v>
+        <v>4553148000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>58500454000</v>
+        <v>42415322000</v>
       </c>
       <c r="AK4" t="n">
-        <v>13430026000</v>
+        <v>6808874000</v>
       </c>
       <c r="AL4" t="n">
-        <v>918404000</v>
+        <v>1063212000</v>
       </c>
       <c r="AM4" t="n">
-        <v>41360000</v>
+        <v>580000</v>
       </c>
       <c r="AN4" t="n">
-        <v>41360000</v>
+        <v>580000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2620851000</v>
+        <v>1701625000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2576293000</v>
+        <v>1673597000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>44558000</v>
+        <v>28028000</v>
       </c>
       <c r="AR4" t="n">
-        <v>2794240000</v>
+        <v>2377500000</v>
       </c>
       <c r="AS4" t="n">
-        <v>19613000</v>
+        <v>20834000</v>
       </c>
       <c r="AT4" t="n">
-        <v>362632000</v>
+        <v>383951000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-212187000</v>
+        <v>-228563000</v>
       </c>
       <c r="AV4" t="n">
-        <v>574819000</v>
+        <v>612514000</v>
       </c>
       <c r="AW4" t="n">
-        <v>63749000</v>
+        <v>62653000</v>
       </c>
       <c r="AX4" t="n">
-        <v>511070000</v>
+        <v>549861000</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>45070428000</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
+        <v>35606448000</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>1027897000</v>
+        <v>391073000</v>
       </c>
       <c r="BC4" t="n">
-        <v>2208568000</v>
+        <v>2379738000</v>
       </c>
       <c r="BD4" t="n">
-        <v>34599754000</v>
+        <v>24219391000</v>
       </c>
       <c r="BE4" t="n">
-        <v>928644000</v>
+        <v>651151000</v>
       </c>
       <c r="BF4" t="n">
-        <v>33671110000</v>
+        <v>23568240000</v>
       </c>
       <c r="BG4" t="n">
-        <v>6354946000</v>
+        <v>7934124000</v>
       </c>
       <c r="BH4" t="n">
-        <v>336931000</v>
+        <v>390210000</v>
       </c>
       <c r="BI4" t="n">
-        <v>542332000</v>
+        <v>291912000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>542332000</v>
+        <v>291912000</v>
       </c>
       <c r="BK4" t="n">
-        <v>542332000</v>
+        <v>291912000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2794994000</v>
+        <v>2794994650</v>
       </c>
       <c r="C5" t="n">
-        <v>2794994000</v>
+        <v>2794994650</v>
       </c>
       <c r="D5" t="n">
-        <v>22961364000</v>
+        <v>23596991000</v>
       </c>
       <c r="E5" t="n">
-        <v>24546407000</v>
+        <v>23684157000</v>
       </c>
       <c r="F5" t="n">
-        <v>4447107000</v>
+        <v>-21999810000</v>
       </c>
       <c r="G5" t="n">
-        <v>29015288000</v>
+        <v>1704265000</v>
       </c>
       <c r="H5" t="n">
-        <v>-4888821000</v>
+        <v>-26856906000</v>
       </c>
       <c r="I5" t="n">
-        <v>4447107000</v>
+        <v>-21999810000</v>
       </c>
       <c r="J5" t="n">
-        <v>4468881000</v>
+        <v>-21979892000</v>
       </c>
       <c r="K5" t="n">
-        <v>6376208000</v>
+        <v>-20098575000</v>
       </c>
       <c r="L5" t="n">
-        <v>6813355000</v>
+        <v>-22649773000</v>
       </c>
       <c r="M5" t="n">
-        <v>2344474000</v>
+        <v>-669881000</v>
       </c>
       <c r="N5" t="n">
-        <v>4468881000</v>
+        <v>-21979892000</v>
       </c>
       <c r="O5" t="n">
-        <v>8612000</v>
+        <v>5640000</v>
       </c>
       <c r="P5" t="n">
         <v>40060000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2599001000</v>
+        <v>-23674252000</v>
       </c>
       <c r="R5" t="n">
         <v>825711000</v>
@@ -2193,131 +2195,129 @@
         <v>175693000</v>
       </c>
       <c r="U5" t="n">
-        <v>70805210000</v>
+        <v>58282481000</v>
       </c>
       <c r="V5" t="n">
-        <v>2560861000</v>
+        <v>2191988000</v>
       </c>
       <c r="W5" t="n">
-        <v>653534000</v>
+        <v>310671000</v>
       </c>
       <c r="X5" t="n">
-        <v>1907327000</v>
+        <v>1881317000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1907327000</v>
+        <v>1881317000</v>
       </c>
       <c r="Z5" t="n">
-        <v>68244349000</v>
+        <v>56090493000</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>22639080000</v>
+        <v>21802840000</v>
       </c>
       <c r="AC5" t="n">
-        <v>22639080000</v>
+        <v>21802840000</v>
       </c>
       <c r="AD5" t="n">
-        <v>264315000</v>
+        <v>795384000</v>
       </c>
       <c r="AE5" t="n">
-        <v>14561175000</v>
+        <v>22185256000</v>
       </c>
       <c r="AF5" t="n">
-        <v>7054457000</v>
+        <v>11638438000</v>
       </c>
       <c r="AG5" t="n">
-        <v>2898000</v>
+        <v>1458000</v>
       </c>
       <c r="AH5" t="n">
-        <v>3940008000</v>
+        <v>5134435000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3563812000</v>
+        <v>5410925000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>77618565000</v>
+        <v>35632708000</v>
       </c>
       <c r="AK5" t="n">
-        <v>14263037000</v>
+        <v>6399121000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1311796000</v>
+        <v>1022784000</v>
       </c>
       <c r="AM5" t="n">
-        <v>46083000</v>
+        <v>1883000</v>
       </c>
       <c r="AN5" t="n">
-        <v>46083000</v>
+        <v>1883000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2337834000</v>
+        <v>1778998000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2233385000</v>
+        <v>1751739000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>104449000</v>
+        <v>27259000</v>
       </c>
       <c r="AR5" t="n">
-        <v>3061710000</v>
+        <v>2010805000</v>
       </c>
       <c r="AS5" t="n">
-        <v>21774000</v>
+        <v>19918000</v>
       </c>
       <c r="AT5" t="n">
-        <v>395700000</v>
+        <v>361409000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-223764000</v>
+        <v>-248499000</v>
       </c>
       <c r="AV5" t="n">
-        <v>619464000</v>
+        <v>609908000</v>
       </c>
       <c r="AW5" t="n">
-        <v>68348000</v>
+        <v>61590000</v>
       </c>
       <c r="AX5" t="n">
-        <v>551116000</v>
+        <v>548318000</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>63355528000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2947689000</v>
-      </c>
+        <v>29233587000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>2426926000</v>
+        <v>250462000</v>
       </c>
       <c r="BC5" t="n">
-        <v>2975285000</v>
+        <v>2325834000</v>
       </c>
       <c r="BD5" t="n">
-        <v>45700454000</v>
+        <v>20295094000</v>
       </c>
       <c r="BE5" t="n">
-        <v>1052545000</v>
+        <v>610930000</v>
       </c>
       <c r="BF5" t="n">
-        <v>44647909000</v>
+        <v>19684164000</v>
       </c>
       <c r="BG5" t="n">
-        <v>7325917000</v>
+        <v>5875772000</v>
       </c>
       <c r="BH5" t="n">
-        <v>394214000</v>
+        <v>399259000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1585043000</v>
+        <v>87166000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1585043000</v>
+        <v>87166000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1585043000</v>
+        <v>87166000</v>
       </c>
     </row>
   </sheetData>
@@ -2598,600 +2598,600 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-394426000</v>
+        <v>-5343773000</v>
       </c>
       <c r="C2" t="n">
-        <v>-30801000</v>
+        <v>-13626212000</v>
       </c>
       <c r="D2" t="n">
-        <v>89150000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>14049203000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-10183000</v>
+      </c>
       <c r="F2" t="n">
-        <v>87166000</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>1585043000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-101595000</v>
+      </c>
       <c r="H2" t="n">
-        <v>291912000</v>
+        <v>10822373000</v>
       </c>
       <c r="I2" t="n">
-        <v>79000</v>
+        <v>1249000</v>
       </c>
       <c r="J2" t="n">
-        <v>-204825000</v>
+        <v>-9136984000</v>
       </c>
       <c r="K2" t="n">
-        <v>38203000</v>
+        <v>-2533635000</v>
       </c>
       <c r="L2" t="n">
-        <v>131000</v>
+        <v>-570636000</v>
       </c>
       <c r="M2" t="n">
-        <v>-20277000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-2300491000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-85499000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-85499000</v>
+      </c>
       <c r="P2" t="n">
-        <v>58349000</v>
+        <v>422991000</v>
       </c>
       <c r="Q2" t="n">
-        <v>58349000</v>
+        <v>422991000</v>
       </c>
       <c r="R2" t="n">
-        <v>-30801000</v>
+        <v>-13626212000</v>
       </c>
       <c r="S2" t="n">
-        <v>89150000</v>
+        <v>14049203000</v>
       </c>
       <c r="T2" t="n">
-        <v>151398000</v>
+        <v>-1269759000</v>
       </c>
       <c r="U2" t="n">
-        <v>140611000</v>
+        <v>705178000</v>
       </c>
       <c r="V2" t="n">
-        <v>18017000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+        <v>67965000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>180000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>180000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>135610000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>135610000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-6415000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>-773259000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>92783000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-6415000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+        <v>-866042000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-7934000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-7934000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>26638000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>28887000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-2249000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-394426000</v>
+        <v>-5333590000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-80000</v>
+        <v>-1166638000</v>
       </c>
       <c r="AL2" t="n">
-        <v>118694000</v>
+        <v>-4326935000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2324778000</v>
+        <v>5973302000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1225967000</v>
+        <v>-1983835000</v>
       </c>
       <c r="AO2" t="n">
-        <v>3588004000</v>
+        <v>-6005139000</v>
       </c>
       <c r="AP2" t="n">
-        <v>81435000</v>
+        <v>-2311263000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2216458000</v>
+        <v>235154000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1933000</v>
+        <v>4175000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2256111000</v>
+        <v>581973000</v>
       </c>
       <c r="AT2" t="n">
-        <v>43067000</v>
+        <v>23989000</v>
       </c>
       <c r="AU2" t="n">
-        <v>2007000</v>
+        <v>3127000</v>
       </c>
       <c r="AV2" t="n">
-        <v>41060000</v>
+        <v>20862000</v>
       </c>
       <c r="AW2" t="n">
-        <v>318547000</v>
+        <v>107215000</v>
       </c>
       <c r="AX2" t="n">
-        <v>181895000</v>
+        <v>-136344000</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>-5718000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1239827000</v>
+        <v>62880000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-7162404000</v>
+        <v>-1562462000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-862256000</v>
+        <v>815889000</v>
       </c>
       <c r="C3" t="n">
-        <v>-783683000</v>
+        <v>-2274309000</v>
       </c>
       <c r="D3" t="n">
-        <v>185000000</v>
+        <v>515800000</v>
       </c>
       <c r="E3" t="n">
-        <v>-377000</v>
+        <v>-1178000</v>
       </c>
       <c r="F3" t="n">
-        <v>291912000</v>
+        <v>542332000</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>542332000</v>
+        <v>1585043000</v>
       </c>
       <c r="I3" t="n">
-        <v>252000</v>
+        <v>-5161000</v>
       </c>
       <c r="J3" t="n">
-        <v>-250672000</v>
+        <v>-1037550000</v>
       </c>
       <c r="K3" t="n">
-        <v>111699000</v>
+        <v>-2545894000</v>
       </c>
       <c r="L3" t="n">
-        <v>831791000</v>
+        <v>-30670000</v>
       </c>
       <c r="M3" t="n">
-        <v>-121409000</v>
+        <v>-756715000</v>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
-        <v>-598683000</v>
+        <v>-1758509000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-598683000</v>
+        <v>-1758509000</v>
       </c>
       <c r="R3" t="n">
-        <v>-783683000</v>
+        <v>-2274309000</v>
       </c>
       <c r="S3" t="n">
-        <v>185000000</v>
+        <v>515800000</v>
       </c>
       <c r="T3" t="n">
-        <v>499508000</v>
+        <v>691277000</v>
       </c>
       <c r="U3" t="n">
-        <v>636824000</v>
+        <v>1537281000</v>
       </c>
       <c r="V3" t="n">
-        <v>19082000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+        <v>10320000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>8485000</v>
+        <v>180770000</v>
       </c>
       <c r="AA3" t="n">
-        <v>8485000</v>
+        <v>180770000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-136964000</v>
+        <v>-1070642000</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>-136964000</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+        <v>-1070642000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
       <c r="AG3" t="n">
-        <v>-272000</v>
+        <v>3924000</v>
       </c>
       <c r="AH3" t="n">
-        <v>105000</v>
+        <v>5102000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-377000</v>
+        <v>-1178000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-861879000</v>
+        <v>817067000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-33124000</v>
+        <v>-234228000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1422040000</v>
+        <v>1966706000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-6353197000</v>
+        <v>312884000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2150539000</v>
+        <v>137393000</v>
       </c>
       <c r="AO3" t="n">
-        <v>7537260000</v>
+        <v>2807034000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1912562000</v>
+        <v>-1290605000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2833871000</v>
+        <v>365373000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-3590000</v>
+        <v>2551000</v>
       </c>
       <c r="AS3" t="n">
-        <v>5835711000</v>
+        <v>634231000</v>
       </c>
       <c r="AT3" t="n">
-        <v>27169000</v>
+        <v>22592000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2080000</v>
+        <v>2161000</v>
       </c>
       <c r="AV3" t="n">
-        <v>25089000</v>
+        <v>20431000</v>
       </c>
       <c r="AW3" t="n">
-        <v>307155000</v>
+        <v>89380000</v>
       </c>
       <c r="AX3" t="n">
-        <v>174071000</v>
+        <v>810441000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-2389000</v>
+        <v>7803000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1004667000</v>
+        <v>929154000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-15529378000</v>
+        <v>-4666803000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>815889000</v>
+        <v>-862256000</v>
       </c>
       <c r="C4" t="n">
-        <v>-2274309000</v>
+        <v>-783683000</v>
       </c>
       <c r="D4" t="n">
-        <v>515800000</v>
+        <v>185000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1178000</v>
+        <v>-377000</v>
       </c>
       <c r="F4" t="n">
-        <v>542332000</v>
+        <v>291912000</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1585043000</v>
+        <v>542332000</v>
       </c>
       <c r="I4" t="n">
-        <v>-5161000</v>
+        <v>252000</v>
       </c>
       <c r="J4" t="n">
-        <v>-1037550000</v>
+        <v>-250672000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2545894000</v>
+        <v>111699000</v>
       </c>
       <c r="L4" t="n">
-        <v>-30670000</v>
+        <v>831791000</v>
       </c>
       <c r="M4" t="n">
-        <v>-756715000</v>
+        <v>-121409000</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-1758509000</v>
+        <v>-598683000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1758509000</v>
+        <v>-598683000</v>
       </c>
       <c r="R4" t="n">
-        <v>-2274309000</v>
+        <v>-783683000</v>
       </c>
       <c r="S4" t="n">
-        <v>515800000</v>
+        <v>185000000</v>
       </c>
       <c r="T4" t="n">
-        <v>691277000</v>
+        <v>499508000</v>
       </c>
       <c r="U4" t="n">
-        <v>1537281000</v>
+        <v>636824000</v>
       </c>
       <c r="V4" t="n">
-        <v>10320000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
+        <v>19082000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>180770000</v>
+        <v>8485000</v>
       </c>
       <c r="AA4" t="n">
-        <v>180770000</v>
+        <v>8485000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1070642000</v>
+        <v>-136964000</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-1070642000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
+        <v>-136964000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>3924000</v>
+        <v>-272000</v>
       </c>
       <c r="AH4" t="n">
-        <v>5102000</v>
+        <v>105000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1178000</v>
+        <v>-377000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>817067000</v>
+        <v>-861879000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-234228000</v>
+        <v>-33124000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1966706000</v>
+        <v>1422040000</v>
       </c>
       <c r="AM4" t="n">
-        <v>312884000</v>
+        <v>-6353197000</v>
       </c>
       <c r="AN4" t="n">
-        <v>137393000</v>
+        <v>2150539000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2807034000</v>
+        <v>7537260000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1290605000</v>
+        <v>-1912562000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>365373000</v>
+        <v>2833871000</v>
       </c>
       <c r="AR4" t="n">
-        <v>2551000</v>
+        <v>-3590000</v>
       </c>
       <c r="AS4" t="n">
-        <v>634231000</v>
+        <v>5835711000</v>
       </c>
       <c r="AT4" t="n">
-        <v>22592000</v>
+        <v>27169000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2161000</v>
+        <v>2080000</v>
       </c>
       <c r="AV4" t="n">
-        <v>20431000</v>
+        <v>25089000</v>
       </c>
       <c r="AW4" t="n">
-        <v>89380000</v>
+        <v>307155000</v>
       </c>
       <c r="AX4" t="n">
-        <v>810441000</v>
+        <v>174071000</v>
       </c>
       <c r="AY4" t="n">
-        <v>7803000</v>
+        <v>-2389000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>929154000</v>
+        <v>1004667000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-4666803000</v>
+        <v>-15529378000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-5343773000</v>
+        <v>-394426000</v>
       </c>
       <c r="C5" t="n">
-        <v>-13626212000</v>
+        <v>-30801000</v>
       </c>
       <c r="D5" t="n">
-        <v>14049203000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-10183000</v>
-      </c>
+        <v>89150000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1585043000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-101595000</v>
-      </c>
+        <v>87166000</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>10822373000</v>
+        <v>291912000</v>
       </c>
       <c r="I5" t="n">
-        <v>1249000</v>
+        <v>79000</v>
       </c>
       <c r="J5" t="n">
-        <v>-9136984000</v>
+        <v>-204825000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2533635000</v>
+        <v>38203000</v>
       </c>
       <c r="L5" t="n">
-        <v>-570636000</v>
+        <v>131000</v>
       </c>
       <c r="M5" t="n">
-        <v>-2300491000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-85499000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-85499000</v>
-      </c>
+        <v>-20277000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>422991000</v>
+        <v>58349000</v>
       </c>
       <c r="Q5" t="n">
-        <v>422991000</v>
+        <v>58349000</v>
       </c>
       <c r="R5" t="n">
-        <v>-13626212000</v>
+        <v>-30801000</v>
       </c>
       <c r="S5" t="n">
-        <v>14049203000</v>
+        <v>89150000</v>
       </c>
       <c r="T5" t="n">
-        <v>-1269759000</v>
+        <v>151398000</v>
       </c>
       <c r="U5" t="n">
-        <v>705178000</v>
+        <v>140611000</v>
       </c>
       <c r="V5" t="n">
-        <v>67965000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>180000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>180000</v>
-      </c>
-      <c r="Y5" t="n">
+        <v>18017000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="n">
-        <v>135610000</v>
-      </c>
       <c r="AA5" t="n">
-        <v>135610000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-773259000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>92783000</v>
-      </c>
+        <v>-6415000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>-866042000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-7934000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-7934000</v>
-      </c>
+        <v>-6415000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>26638000</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>28887000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2249000</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-5333590000</v>
+        <v>-394426000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1166638000</v>
+        <v>-80000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-4326935000</v>
+        <v>118694000</v>
       </c>
       <c r="AM5" t="n">
-        <v>5973302000</v>
+        <v>-2324778000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1983835000</v>
+        <v>-1225967000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-6005139000</v>
+        <v>3588004000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-2311263000</v>
+        <v>81435000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>235154000</v>
+        <v>2216458000</v>
       </c>
       <c r="AR5" t="n">
-        <v>4175000</v>
+        <v>-1933000</v>
       </c>
       <c r="AS5" t="n">
-        <v>581973000</v>
+        <v>2256111000</v>
       </c>
       <c r="AT5" t="n">
-        <v>23989000</v>
+        <v>43067000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3127000</v>
+        <v>2007000</v>
       </c>
       <c r="AV5" t="n">
-        <v>20862000</v>
+        <v>41060000</v>
       </c>
       <c r="AW5" t="n">
-        <v>107215000</v>
+        <v>318547000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-136344000</v>
+        <v>181895000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-5718000</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>62880000</v>
+        <v>1239827000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-1562462000</v>
+        <v>-7162404000</v>
       </c>
     </row>
   </sheetData>
@@ -3736,82 +3736,82 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="DR1" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Peng  Zhang', 'age': 50, 'title': 'CEO, President &amp; Executive Chairman', 'yearBorn': 1975, 'fiscalYear': 2024, 'totalPay': 1048118, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Lei  Zhang', 'age': 63, 'title': 'Executive Director', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 1028430, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yin  Chen', 'age': 70, 'title': 'CTO, Head of Research &amp; Development Department and Executive Director', 'yearBorn': 1955, 'fiscalYear': 2024, 'totalPay': 456308, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wang  Qiang', 'age': 52, 'title': 'Senior Vice President', 'yearBorn': 1973, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shihong  Zhang', 'title': 'Senior Vice President', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yang  Guang', 'title': 'Senior Vice President', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Feng  JinLong', 'title': 'Executive Vice President', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Lei  Zhixin', 'title': 'Executive President', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Han  Feiyu', 'title': 'Senior Vice President', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwan Long  Wong', 'age': 42, 'title': 'Company Secretary', 'yearBorn': 1983, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Peng  Zhang', 'age': 50, 'title': 'CEO, President &amp; Executive Chairman', 'yearBorn': 1975, 'fiscalYear': 2024, 'totalPay': 1047554, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Lei  Zhang', 'age': 63, 'title': 'Executive Director', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 1027876, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yin  Chen', 'age': 70, 'title': 'CTO, Head of Research &amp; Development Department and Executive Director', 'yearBorn': 1955, 'fiscalYear': 2024, 'totalPay': 456062, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wang  Qiang', 'age': 52, 'title': 'Senior Vice President', 'yearBorn': 1973, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shihong  Zhang', 'title': 'Senior Vice President', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yang  Guang', 'title': 'Senior Vice President', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Feng  JinLong', 'title': 'Executive Vice President', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Lei  Zhixin', 'title': 'Executive President', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Han  Feiyu', 'title': 'Senior Vice President', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwan Long  Wong', 'age': 42, 'title': 'Company Secretary', 'yearBorn': 1983, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4067,7 +4067,7 @@
         <v>10.04</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.115</v>
+        <v>1.123</v>
       </c>
       <c r="AH2" t="n">
         <v>0.030232558</v>
@@ -4079,7 +4079,7 @@
         <v>11186000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3226477</v>
+        <v>1301084</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         <v>0.014268224</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.01342</v>
+        <v>0.013</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.018225</v>
+        <v>0.017705</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -4156,13 +4156,13 @@
         <v>0.66563004</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.06819</v>
+        <v>0.06804</v>
       </c>
       <c r="BK2" t="n">
         <v>2794994650</v>
       </c>
       <c r="BL2" t="n">
-        <v>-9.5454235</v>
+        <v>-9.561173999999999</v>
       </c>
       <c r="BM2" t="n">
         <v>1735603200</v>
@@ -4200,7 +4200,7 @@
         <v>-0.38095236</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="n">
         <v>0.0365</v>
@@ -4307,15 +4307,11 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>MODERN LAND</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>Modern Land (China) Co., Limited</t>
-        </is>
+      <c r="DB2" t="n">
+        <v>-7.142858</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.013</v>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
@@ -4327,51 +4323,55 @@
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>finmb_115032605</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>finmb_115032605</t>
+          <t>Asia/Hong_Kong</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DK2" t="n">
+      <c r="DJ2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="DL2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="n">
-        <v>-7.142858</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="DP2" t="b">
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>MODERN LAND</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Modern Land (China) Co., Limited</t>
+        </is>
+      </c>
+      <c r="DO2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DP2" t="n">
         <v>1373592600000</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="DR2" t="n">
         <v>-0.0010000002</v>
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="DU2" t="n">
-        <v>3226477</v>
+        <v>1301084</v>
       </c>
       <c r="DV2" t="n">
         <v>0.0020000003</v>
@@ -4425,19 +4425,19 @@
         <v>0.43</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.00041999947</v>
+        <v>0</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0.031296533</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.005224999</v>
+        <v>-0.004704999</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.28669405</v>
+        <v>-0.2657441</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0.0013619092</v>
+        <v>-0.0013596656</v>
       </c>
       <c r="EL2" t="n">
         <v>15</v>
